--- a/datasets/Dataset_S5_Curated_TFs.xlsx
+++ b/datasets/Dataset_S5_Curated_TFs.xlsx
@@ -685,7 +685,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>manual search (CDD), family level</t>
+          <t>conserved-domain family (CDD)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>manual search (uniprot/CDD); 7942 Xre1 is RS09740</t>
+          <t>XRE family (CDD); paralogs numbered within the species</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dnaA</t>
+          <t>DnaA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sigC</t>
+          <t>SigA5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>literature, see Table 4; curated (Dataset S5)</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Imamura and Asayama 2009, group E sigma factor SigC (SYNPCC7002_A0364); PCC 7942 SigA5 product name also reads SigC, different ortholog group</t>
+          <t>Imamura and Asayama 2009; group-2 E-type sigma factor (SYNPCC7002_A0364)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>nusA</t>
+          <t>NusA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PhoB-like OmpR-family response regulator (CDD TIGR02154); ortholog of PCC 7942 SphR (Synpcc7942_1012) and PCC 6803 SphR (slr0081), 64% identity</t>
+          <t>ortholog of SphR in PCC 7942 and PCC 6803 (Dataset S5-4)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nrdR</t>
+          <t>NrdR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ortholog of NtcA, tri-homolog with SYNPCC7942_RS00645 and SGL_RS09285</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>pyrR</t>
+          <t>PyrR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>sfsA</t>
+          <t>SfsA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sufR</t>
+          <t>SufR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lexA</t>
+          <t>LexA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>manual search (CDD), family level</t>
+          <t>conserved-domain family (CDD)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NarL family (CDD v3.21); numbered within PCC 7002</t>
+          <t>NarL family (CDD); paralogs numbered within the species</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4952,7 +4952,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>hrcA</t>
+          <t>HrcA</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>NarL family; numbered within PCC 7002</t>
+          <t>NarL family (CDD); paralogs numbered within the species</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>literature, see Table 4; curated (Dataset S5)</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>literature, see Table 4; curated (Dataset S5)</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nusG</t>
+          <t>NusG</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>rpoD</t>
+          <t>SigA1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lexA</t>
+          <t>LexA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>manual search; slr0312, also published as Rre32 (Huokko 2019)</t>
+          <t>NarL family (CDD); paralogs numbered within the species; also named Rre32</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>hrcA</t>
+          <t>HrcA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>manual search (UniProt/CDD, NarL subfamily); numbered by locus order</t>
+          <t>NarL family (CDD); paralogs numbered within the species</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sigC</t>
+          <t>SigA5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>pyrR</t>
+          <t>PyrR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>nrdR</t>
+          <t>NrdR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>nusA</t>
+          <t>NusA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>manual search</t>
+          <t>conserved-domain family (CDD)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sfsA</t>
+          <t>SfsA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>curated (Datasets S5, S6)</t>
+          <t>core GRN name (Dataset S6-2)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sufR</t>
+          <t>SufR</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7936,7 +7936,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>kaiC</t>
+          <t>KaiC2</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>nusB</t>
+          <t>NusB</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>dnaA</t>
+          <t>DnaA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>literature, see Table 4</t>
+          <t>literature (Table 4)</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
